--- a/Planning_Docs/AX_Bridge_DB_API_명세서.xlsx
+++ b/Planning_Docs/AX_Bridge_DB_API_명세서.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -547,14 +547,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AX Bridge — DB 오브젝트 · API Gateway 명세서</t>
+          <t>AX Bridge — DB 오브젝트 · API 명세서</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>작성일 2026-08-13 · v2.0 · 근거: 화면기획서 4종(FINANCE v3.0 반영) + AX_Bridge.xlsx(FR/UC)</t>
+          <t>작성일 2026-08-14 · v3.0 · 근거: 화면기획서 4종(FINANCE v3.0 반영) + AX_Bridge.xlsx(FR/UC) + 구현 코드 검토(apps/api · apps/web)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>AX Bridge MSSQL 프로시저·트리거 명세서 및 API Gateway 명세서</t>
+          <t>AX Bridge MSSQL 프로시저·트리거 명세서 및 API 명세서 (구현 대조본)</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>AX_Bridge.xlsx (테이블명세·FR·UC·표준 GL seed), SYSTEM/PARTNER/SALES/FINANCE 화면기획서 v1.0~v2.1</t>
+          <t>AX_Bridge.xlsx(테이블명세·FR·UC·표준 GL seed), SYSTEM/PARTNER/SALES/FINANCE 화면기획서 v1.0~v2.1, 01~09 SQL 스크립트, 구현 코드(apps/api 컨트롤러 94건 · apps/web 화면 17종)</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>01 Tables(DDL+Bootstrap) → 02~05 Procs(SYSTEM/PARTNER/SALES/FINANCE) → 06 Triggers → 07 Seed GL → 08 Update v3 Finance (마감관리·초기이월 bank_id 개정 — 01~07 적용 후 실행)</t>
+          <t>01 Tables(DDL+Bootstrap) → 02~05 Procs(SYSTEM/PARTNER/SALES/FINANCE) → 06 Triggers → 07 Seed GL → 08 Update v3 Finance(마감관리·초기이월 bank_id 개정) → 09 Fix(결함수정·무결성 보강·마감해제 신설 — 01~08 적용 후 실행). 09 는 멱등하며 반복 실행해도 안전하다.</t>
         </is>
       </c>
     </row>
@@ -723,6 +723,42 @@
       <c r="B17" s="4" t="inlineStr">
         <is>
           <t>50001~ AUTH · 501xx SYSTEM · 502xx PARTNER · 503xx SALES · 504xx FINANCE(프로시저) · 51xxx 트리거</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>구현 현황</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>본 명세는 구현 완료본과 대조 검증되었다(2026-08-14). 백엔드 NestJS Modular Monolith (apps/api, 94 엔드포인트) · 프론트엔드 React+Vite+Ant Design(apps/web, 17 화면) · DB 프로시저 75건 / 트리거 10건. Gateway 는 별도 구축하지 않았고 동일 정책을 NestJS Guard·Interceptor 가 수행한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>설계 결정 6</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>D2(Command/Query 분리) — 조회 성능·화면 요구가 프로시저 반환열을 넘어서는 경우에 한해 Prisma Query Service 를 쓴다. 현재 해당 건은 GET /finance/gl 1건뿐이다: usp_finance_gl_list 가 gl_id·gl_name 2열만 반환하는데 화면기획서 5-1 ② 는 계정구분까지 3열을 요구한다. 부수 효과로 GL 목록에 실제 페이징이 생겼다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>설계 결정 7</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>D4(연도 회계마감 해제) — 원본 산출물에는 마감을 되돌리는 경로가 없었다. 09 에서 usp_finance_closing_reopen 을 신설한다. 마감이 오름차순 순차이므로 해제는 내림차순 순차다. ⚠ 한계 — 해제해도 기존 승인 전표는 편집할 수 없다(승인취소 기능이 원본에 없다).</t>
         </is>
       </c>
     </row>
@@ -737,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -835,6 +871,33 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>v3.0</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>구현 코드 검토 (apps/api · apps/web) + 09_AX_Bridge_Fix.sql</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>① 09_AX_Bridge_Fix.sql 반영 — DDL 무결성 6건(open_balance PK 신설·source 컬럼 신설, bank_account 계좌 XOR 카드 완성·계좌/카드번호 중복 금지, dimension_detail 값 중복 금지, ledger_head.approved_date → datetime2(0)) ② 프로시저 결함 수정 6건 (dimension_delete 트랜잭션화 · gl_generate_standard 의 @@ROWCOUNT 포착 위치 · activity_save 채번 경합 · auth_change_password 트랜잭션 템플릿 · ledger_approve 초 단위 승인시각 · closing_execute 의 source=CLOSING 기록) ③ usp_finance_closing_reopen 신설 — 프로시저 74→75건, 오류코드 50531~50535 ④ API 92→94건 — POST /finance/closings/{yearId}/reopen(09), POST /finance/ledgers/preview-account-change(구현) 추가 ⑤ GET /finance/gl 호출 계층 변경 — usp_finance_gl_list → FinanceQuery(Prisma), 계정구분 3컬럼·페이징(D2) ⑥ API 공통정책을 실제 구현(NestJS Modular Monolith)에 맞게 정정 — Gateway 미구축, Swagger /api/docs 제공</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>09 (+ apps/api · apps/web)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -846,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -864,14 +927,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MSSQL 저장 프로시저 명세 (총 74건)</t>
+          <t>MSSQL 저장 프로시저 명세 (총 75건)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>공통: 세션 기반 회사코드 주입 · @search_mode E/L · @mode I/U · THROW 50xxx 한글 오류 · 노란 표시 = v3.0 신규/개정</t>
+          <t>공통: 세션 기반 회사코드 주입 · @search_mode E/L · @mode I/U · THROW 50xxx 한글 오류. [09] 표기 = 09_AX_Bridge_Fix.sql 에서 수정/신설된 프로시저</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1116,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>새 해시로 교체(빈 해시 거부, user_yn=N 거부). 기존 해시 표시/반환 없음</t>
+          <t>새 해시로 교체(빈 해시 거부, user_yn=N 거부). 기존 해시 표시/반환 없음  [09] 표준 트랜잭션 템플릿(XACT_ABORT+TRY/CATCH) 적용. 검증·오류코드는 동일.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1073,7 +1136,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>02_AX_Bridge_Procs_SYSTEM.sql</t>
+          <t>02_AX_Bridge_Procs_SYSTEM.sql → 09_AX_Bridge_Fix.sql</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3116,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>I: activity_id 시스템생성(ACT+타임스탬프) 또는 고유값, 타입 검증, created_date 기본값. U: 식별키/상위 변경 불가</t>
+          <t>I: activity_id 시스템생성(ACT+타임스탬프) 또는 고유값, 타입 검증, created_date 기본값. U: 식별키/상위 변경 불가  [09] activity_id 채번 경합 방지 — 1/100초 해상도 충돌 시 2자리 일련번호를 덧붙여 재시도(WAITFOR 미사용).</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -3073,7 +3136,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>04_AX_Bridge_Procs_SALES.sql</t>
+          <t>04_AX_Bridge_Procs_SALES.sql → 09_AX_Bridge_Fix.sql</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3616,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>표준 계정과목 재생성. 로그인 회사 전표 존재 시 서버 재검증 후 차단 → 기존 GL 전체삭제 → seed 일괄 INSERT(회사코드만 치환)를 단일 트랜잭션 원자 처리. 실패 시 전체 ROLLBACK</t>
+          <t>표준 계정과목 재생성. 로그인 회사 전표 존재 시 서버 재검증 후 차단 → 기존 GL 전체삭제 → seed 일괄 INSERT(회사코드만 치환)를 단일 트랜잭션 원자 처리. 실패 시 전체 ROLLBACK  [09] inserted_count 오류 수정 — @@ROWCOUNT 를 INSERT 직후에 포착하도록 변경(기존에는 COMMIT 뒤라 항상 무의미한 값).</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3573,7 +3636,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>05_AX_Bridge_Procs_FINANCE.sql</t>
+          <t>05_AX_Bridge_Procs_FINANCE.sql → 09_AX_Bridge_Fix.sql</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3866,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>계정 플래그/전표 값 참조 시 차단(Slot 보존)</t>
+          <t>계정 플래그/전표 값 참조 시 차단(Slot 보존)  [09] 비원자적 DELETE 2회 → 단일 트랜잭션(XACT_ABORT)으로 교체. 검증 로직(50427/50428)은 동일.</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3823,7 +3886,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>05_AX_Bridge_Procs_FINANCE.sql</t>
+          <t>05_AX_Bridge_Procs_FINANCE.sql → 09_AX_Bridge_Fix.sql</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4316,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>[v3.0] 마감연도 승인 불가 검증 추가. 라인 존재·차대변 균형 검증 후 승인 기록</t>
+          <t>[v3.0] 마감연도 승인 불가 검증 추가. 라인 존재·차대변 균형 검증 후 승인 기록  [09] approved_date 를 초 단위로 기록(컬럼 datetime2(0) 승격 동반).</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -4273,7 +4336,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>08_AX_Bridge_Update_v3_Finance.sql</t>
+          <t>08_AX_Bridge_Update_v3_Finance.sql → 09_AX_Bridge_Fix.sql</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4516,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>[v3.0] 연도 회계마감(1개 연도 단위, 복수 선택 시 API가 연도 오름차순 순차 호출). 선행검증 6종(기수·재마감·선행연도·차년도 기수·미승인 전표 0건·차년도 초기이월 미존재) → gl_type 0~2 조합별(gl+bank+client+vendor) 잔액 산출(자산=차변, 부채·자본=대변, 0잔액 미생성) → 차년도 open_balance INSERT(closed=Y) → closing=Y·closing_date 기록. 단일 트랜잭션, 실패 시 전체 ROLLBACK</t>
+          <t>[v3.0] 연도 회계마감(1개 연도 단위, 복수 선택 시 API가 연도 오름차순 순차 호출). 선행검증 6종(기수·재마감·선행연도·차년도 기수·미승인 전표 0건·차년도 초기이월 미존재) → gl_type 0~2 조합별(gl+bank+client+vendor) 잔액 산출(자산=차변, 부채·자본=대변, 0잔액 미생성) → 차년도 open_balance INSERT(closed=Y) → closing=Y·closing_date 기록. 단일 트랜잭션, 실패 시 전체 ROLLBACK  [09] 자동생성 이월에 source='CLOSING' 기록 — 마감해제의 회수 대상 식별 근거.</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -4473,7 +4536,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>08_AX_Bridge_Update_v3_Finance.sql</t>
+          <t>08_AX_Bridge_Update_v3_Finance.sql → 09_AX_Bridge_Fix.sql</t>
         </is>
       </c>
     </row>
@@ -4624,6 +4687,56 @@
       <c r="J77" s="4" t="inlineStr">
         <is>
           <t>05_AX_Bridge_Procs_FINANCE.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>마감관리</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>usp_finance_closing_reopen</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>마감해제</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>[09 신설] 연도 회계마감 해제(ADMIN 전용). 해제는 늦은 연도부터 **내림차순 순차**다. 선행검증 5종 — 기수 존재(50531) · 마감 상태(50532) · 후행연도 미마감(50533) · 차년도 수기 초기이월 부재(50534) · 차년도 전표 0건(50535). 통과 시 closing=0·closing_date=NULL 로 되돌리고 차년도의 source='CLOSING' 이월만 회수한다(수기분 MANUAL 은 보존). ax_openbal_admin 세션 플래그를 쓰므로 단일 커넥션에서 실행해야 한다. 단일 트랜잭션.</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>@company_id,@entity_id,@company_year_id</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>{reopened_year_id, next_year_id, removed_rows}</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>설계서 §9.6(D4), FR-Close-11 보완</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>09_AX_Bridge_Fix.sql</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4775,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>목적: 프로시저 우회 직접 DML로부터 핵심 업무규칙 이중 방어. 스크립트: 06 + 08(교체/신규분). 노란 표시 = v3.0 신규/개정</t>
+          <t>목적: 프로시저 우회 직접 DML로부터 핵심 업무규칙 이중 방어. 스크립트: 06 + 08(교체/신규분). 09 는 트리거를 변경하지 않았다 — 구현 검토 결과 문서 10건과 DB 10건이 일치한다(2026-08-14).</t>
         </is>
       </c>
     </row>
@@ -5184,14 +5297,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>API Gateway 공통 정책</t>
+          <t>API 공통 정책</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v1.0 · 근거: FR-UI-04/07, FR-Emp-04/05, FR-Bank-08, FR-GL-12</t>
+          <t>v3.0 · 근거: FR-UI-04/07, FR-Emp-04/05, FR-Bank-08, FR-GL-12 + 구현 검토(apps/api). ⚠ 별도 API Gateway 는 구축하지 않았다 — 아래 정책은 NestJS Guard·Interceptor 가 수행한다.</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5316,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>https://api.axbridge.example.com/api/v1  (Gateway → 내부 도메인 서비스 라우팅: /auth·/system → system-svc, /partner → partner-svc, /sales → sales-svc, /finance → finance-svc)</t>
+          <t>/api/v1 (NestJS 전역 prefix). Modular Monolith 이므로 도메인별 서비스 분리·Gateway 라우팅은 없다 — /auth·/system·/partner·/sales·/finance 는 같은 프로세스의 모듈이다. 프론트엔드는 Vite dev proxy 로 /api 를 API 서버에 넘긴다. Swagger UI: /api/docs.</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5340,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>company_id/entity_id 는 요청 본문·쿼리로 받지 않고 Gateway가 JWT claim에서 추출하여 백엔드로 전달(헤더 X-Company-Id / X-Entity-Id). 서버가 모든 프로시저 호출 시 재검증 — 화면 조건만으로 권한 판단 금지(FR-Bank-08).</t>
+          <t>company_id/entity_id 는 요청 본문·쿼리로 받지 않는다. JwtAuthGuard 가 JWT claim 에서 꺼내 @Scope() CompanyScope 로 주입하고, 모든 Repository 가 프로시저 파라미터로 넘긴다. 클라이언트 입력값은 신뢰하지 않는다(FR-Bank-08).</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5352,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>VIEWER(조회) &lt; EDITOR(등록/수정/삭제) &lt; APPROVER(전표 승인) &lt; ADMIN(마감해제·표준GL생성·비밀번호 초기화) &lt; SUPER(admin). 조회전용 사용자는 편집 API 403(FR-UI-07).</t>
+          <t>VIEWER(조회) &lt; EDITOR(등록/수정/삭제) &lt; APPROVER(전표 승인) &lt; ADMIN(마감·마감해제·표준GL생성·비밀번호 초기화) &lt; SUPER(admin). 엔드포인트마다 @MinRole(Role.X) 로 최소 등급을 선언하고 RolesGuard 가 계층 비교로 판정한다. 조회전용 사용자는 편집 API 403(FR-UI-07).</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5376,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>{ "success": bool, "data": …, "error": { "code": "AX-50xxx", "message": "한글 메시지" } }  — DB THROW 오류번호를 AX-코드로 매핑하여 그대로 전달.</t>
+          <t>{ "success": true, "data": … } / 실패 시 { "success": false, "error": { "code": "AX-50xxx", "message": "한글 메시지" } }. ApiResponseInterceptor 가 감싸고 AllExceptionsFilter 가 DB THROW 번호를 AX- 코드로 매핑한다.</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5388,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>200 조회/수정 · 201 등록 · 204 삭제 · 400 검증오류(50xxx) · 401 미인증 · 403 권한없음 · 404 대상없음 · 409 중복/참조충돌 · 500 서버오류.</t>
+          <t>200 조회/수정 · 201 등록 · 204 삭제 · 400 검증오류(50xxx) · 401 미인증 · 403 권한없음 · 404 대상없음 · 409 중복/참조충돌 · 500 서버오류. 429 Rate Limit 초과.</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5400,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>사용자당 120 req/min (Gateway 계층). 초과 시 429 + Retry-After.</t>
+          <t>사용자당 120 req/min (RATE_LIMIT_PER_MIN 환경변수, ttl 60초). @nestjs/throttler 의 ThrottlerGuard 를 전역 APP_GUARD 로 적용한다 — Guard 순서는 인증(JwtAuthGuard) → 권한(RolesGuard) → Rate Limit. 초과 시 429.</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5412,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>모든 쓰기 요청은 user_id·IP·요청경로·결과코드를 Gateway 액세스로그에 기록. 비밀번호 필드는 로그 마스킹(FR-Emp-04).</t>
+          <t>AuditInterceptor 가 쓰기 요청의 user_id·요청경로·결과를 기록한다. 비밀번호 필드는 DTO 단계에서 마스킹되어 로그에 남지 않는다(FR-Emp-04).</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5345,14 +5458,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>API Gateway 엔드포인트 명세 (총 92건)</t>
+          <t>API 엔드포인트 명세 (총 94건)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>모든 엔드포인트 인증 필수(공개 표기 제외) · company/entity 는 JWT claim 서버 주입 · 오류 AX-50xxx 매핑 · 노란 표시 = v3.0 신규/개정</t>
+          <t>모든 엔드포인트 인증 필수(공개 표기 제외) · company/entity 는 JWT claim 서버 주입 · 오류 AX-50xxx 매핑 · [구현] 표기 = 2026-08-14 구현 검토에서 추가/정정된 행</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8917,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>계정 배열</t>
+          <t>{items[], page, size, total}</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -8814,7 +8927,7 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_gl_list</t>
+          <t>FinanceQuery(Prisma) — [구현] usp_finance_gl_list 는 gl_id·gl_name 2열만 반환하지만 화면기획서 5-1 ② 는 계정구분까지 3열을 요구한다. D2 원칙대로 Query Service 가 담당하며 부수 효과로 페이징이 생겼다. (프로시저는 DB 에 남아 있으나 애플리케이션은 호출하지 않는다)</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -9772,99 +9885,99 @@
           <t>전표관리</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>/finance/ledgers/preview-account-change</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>[구현] 계정 변경 시 버려질 Layer3 값 미리보기(UC-Ledger-04 예외). 플래그가 Y→N 이 되어 입력할 수 없게 되는 항목 목록만 돌려주고 값을 지우지는 않는다 — 화면이 사용자 확인을 받은 뒤 정리된 라인으로 저장한다. Domain(LedgerLine)이 판정하므로 호출 프로시저가 없다.</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Body: {current_line:{gl_id, DRCR, amount, bank_id?, Team_id?, …}, next_gl_id}</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>{conflicts:[{field, value}], nextFlags}</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>EDITOR</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>-(애플리케이션 Domain 계산)</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>FR-Ledger-06/07, UC-Ledger-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>전표관리</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>/finance/ledgers/{ledgerDate}/{ledgerNo}</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>전표 상세(헤더+라인+Layer3 값+계정 플래그)</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>Path: ledgerDate, ledgerNo</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>{head, lines[]}</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>VIEWER</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>usp_finance_ledger_get</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>UC-Ledger-01/04</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="16" t="n">
-        <v>81</v>
-      </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t>FINANCE</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>전표관리</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>/finance/ledgers</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>[v3.0] 전표 Head 등록(ledger_no 자동부여, 승인상태 N). 회계마감 연도 409(FR-Ledger-16)</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>Body: {ledger_date, ledger_name?, ledger_type}</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>201 + {ledger_no}</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>EDITOR</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>usp_finance_ledger_head_save(I)</t>
-        </is>
-      </c>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t>UC-Ledger-02</t>
         </is>
       </c>
     </row>
@@ -9882,29 +9995,29 @@
           <t>전표관리</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>/finance/ledgers/{ledgerDate}/{ledgerNo}</t>
+          <t>/finance/ledgers</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>[v3.0] 전표 Head 수정(미승인만). 회계마감 연도 409</t>
+          <t>[v3.0] 전표 Head 등록(ledger_no 자동부여, 승인상태 N). 회계마감 연도 409(FR-Ledger-16)</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Body: {ledger_name, ledger_type}</t>
+          <t>Body: {ledger_date, ledger_name?, ledger_type}</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201 + {ledger_no}</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -9914,12 +10027,12 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_ledger_head_save(U)</t>
+          <t>usp_finance_ledger_head_save(I)</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>UC-Ledger-09</t>
+          <t>UC-Ledger-02</t>
         </is>
       </c>
     </row>
@@ -9944,17 +10057,17 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>/finance/ledgers/{ledgerDate}/{ledgerNo}/lines</t>
+          <t>/finance/ledgers/{ledgerDate}/{ledgerNo}</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>[v3.0] 전표 라인 일괄 저장(플래그·Slot·bank·due_date 검증). 회계마감 연도 409</t>
+          <t>[v3.0] 전표 Head 수정(미승인만). 회계마감 연도 409</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Body: {lines:[{gl_id, DRCR, amount, bank_id?, Team_id?, …, due_date?}]}</t>
+          <t>Body: {ledger_name, ledger_type}</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -9969,12 +10082,12 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_ledger_detail_save</t>
+          <t>usp_finance_ledger_head_save(U)</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>UC-Ledger-03/04/05/07/12</t>
+          <t>UC-Ledger-09</t>
         </is>
       </c>
     </row>
@@ -9992,44 +10105,44 @@
           <t>전표관리</t>
         </is>
       </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>/finance/ledgers/{ledgerDate}/{ledgerNo}/approve</t>
+          <t>/finance/ledgers/{ledgerDate}/{ledgerNo}/lines</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>[v3.0] 전표 승인(차대변 균형 검증). 회계마감 연도 승인 불가 409</t>
+          <t>[v3.0] 전표 라인 일괄 저장(플래그·Slot·bank·due_date 검증). 회계마감 연도 409</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Body: {lines:[{gl_id, DRCR, amount, bank_id?, Team_id?, …, due_date?}]}</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>APPROVER</t>
+          <t>EDITOR</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_ledger_approve</t>
+          <t>usp_finance_ledger_detail_save</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>UC-Ledger-08/11</t>
+          <t>UC-Ledger-03/04/05/07/12</t>
         </is>
       </c>
     </row>
@@ -10047,19 +10160,19 @@
           <t>전표관리</t>
         </is>
       </c>
-      <c r="D88" s="14" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>/finance/ledgers/{ledgerDate}/{ledgerNo}</t>
+          <t>/finance/ledgers/{ledgerDate}/{ledgerNo}/approve</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>[v3.0] 전표 삭제(미승인만, 라인+헤더 동시). 회계마감 연도 409</t>
+          <t>[v3.0] 전표 승인(차대변 균형 검증). 회계마감 연도 승인 불가 409</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -10074,17 +10187,17 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>EDITOR</t>
+          <t>APPROVER</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_ledger_delete</t>
+          <t>usp_finance_ledger_approve</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>UC-Ledger-10</t>
+          <t>UC-Ledger-08/11</t>
         </is>
       </c>
     </row>
@@ -10099,47 +10212,47 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>마감관리</t>
-        </is>
-      </c>
-      <c r="D89" s="13" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>전표관리</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>/finance/closings</t>
+          <t>/finance/ledgers/{ledgerDate}/{ledgerNo}</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>[v3.0] 기수·연도별 회계마감 현황(마감여부·마감일자·선행연도 미마감 여부). 행 없으면 미마감으로 표시</t>
+          <t>[v3.0] 전표 삭제(미승인만, 라인+헤더 동시). 회계마감 연도 409</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Query: closing(Y/N/전체)</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>[{company_year_id, company_year, actual_year, closing, closing_date, prior_year_open}]</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>VIEWER</t>
+          <t>EDITOR</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_closing_list</t>
+          <t>usp_finance_ledger_delete</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>FR-Close-01, UC-Close-01</t>
+          <t>UC-Ledger-10</t>
         </is>
       </c>
     </row>
@@ -10157,44 +10270,44 @@
           <t>마감관리</t>
         </is>
       </c>
-      <c r="D90" s="11" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>/finance/closings/{yearId}/execute</t>
+          <t>/finance/closings</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>[v3.0] 연도 회계마감 실행. 복수 연도 체크 시 클라이언트가 연도 오름차순 순차 호출 — 순서 위반·재마감·미승인 전표·차년도 초기이월 존재는 서버 검증으로 400/409. 성공 시 차년도 이월(closed=Y) 생성+closing=Y 기록(단일 트랜잭션)</t>
+          <t>[v3.0] 기수·연도별 회계마감 현황(마감여부·마감일자·선행연도 미마감 여부). 행 없으면 미마감으로 표시</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Path: yearId(company_year_id)</t>
+          <t>Query: closing(Y/N/전체)</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>{closed_year_id, next_year_id, carried_rows}</t>
+          <t>[{company_year_id, company_year, actual_year, closing, closing_date, prior_year_open}]</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>VIEWER</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_closing_execute</t>
+          <t>usp_finance_closing_list</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>FR-Close-02~10, UC-Close-02~06</t>
+          <t>FR-Close-01, UC-Close-01</t>
         </is>
       </c>
     </row>
@@ -10212,114 +10325,114 @@
           <t>마감관리</t>
         </is>
       </c>
-      <c r="D91" s="13" t="inlineStr">
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>/finance/closings/{yearId}/execute</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>[v3.0] 연도 회계마감 실행. 복수 연도 체크 시 클라이언트가 연도 오름차순 순차 호출 — 순서 위반·재마감·미승인 전표·차년도 초기이월 존재는 서버 검증으로 400/409. 성공 시 차년도 이월(closed=Y) 생성+closing=Y 기록(단일 트랜잭션)</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Path: yearId(company_year_id)</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>{closed_year_id, next_year_id, carried_rows}</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>usp_finance_closing_execute</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>FR-Close-02~10, UC-Close-02~06</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>마감관리</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>/finance/closings/{yearId}/status</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>[v3.0] 특정 연도 마감 여부 단건 확인 — 전표/초기이월 화면 진입 시 버튼 비활성 제어용(화면 비활성+서버 검증 병행)</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>Path: yearId</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>{closing, closing_date}</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr">
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>VIEWER</t>
         </is>
       </c>
-      <c r="J91" s="4" t="inlineStr">
+      <c r="J92" s="4" t="inlineStr">
         <is>
           <t>usp_finance_closing_list(필터)</t>
         </is>
       </c>
-      <c r="K91" s="4" t="inlineStr">
+      <c r="K92" s="4" t="inlineStr">
         <is>
           <t>FR-Close-11, FR-Ledger-16, UC-Ledger-13</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>FINANCE</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>은행/카드</t>
-        </is>
-      </c>
-      <c r="D92" s="13" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>/finance/bank-accounts</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>은행/카드 목록(카드번호 마스킹, active_only=전표 팝업)</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>Query: bank_keyword, status, search_mode, active_only</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>목록(마스킹)</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>VIEWER</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>usp_finance_bank_list</t>
-        </is>
-      </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>UC-Bank-01/06</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>FINANCE</t>
-        </is>
-      </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>은행/카드</t>
+          <t>마감관리</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
@@ -10329,37 +10442,37 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>/finance/bank-accounts</t>
+          <t>/finance/closings/{yearId}/reopen</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>은행계좌 또는 카드 등록(상호배타·중복 검증)</t>
+          <t>[09 신설] 연도 회계마감 해제(설계서 §9.6, D4). 해제는 늦은 연도부터 내림차순 순차다. 후행연도가 마감 상태거나(50533) 차년도에 수기 초기이월(50534)·전표(50535)가 있으면 거부. 성공 시 closing=N 으로 되돌리고 차년도의 source='CLOSING' 이월만 회수한다. ⚠ 해제해도 기존 승인 전표는 편집할 수 없다 — 승인취소 기능이 원본에 없다.</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Body: {bank_id, bank_name, bank_account? XOR card_number?, status}</t>
+          <t>Path: yearId(company_year_id)</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>{reopened_year_id, next_year_id, removed_rows}</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>EDITOR</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_bank_save(I)</t>
+          <t>usp_finance_closing_reopen</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>UC-Bank-02/03</t>
+          <t>설계서 §9.6(D4), FR-Close-11 보완</t>
         </is>
       </c>
     </row>
@@ -10377,44 +10490,44 @@
           <t>은행/카드</t>
         </is>
       </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>/finance/bank-accounts/{bankId}</t>
+          <t>/finance/bank-accounts</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>은행/카드 수정/사용여부 변경</t>
+          <t>은행/카드 목록(카드번호 마스킹, active_only=전표 팝업)</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Body: 수정필드</t>
+          <t>Query: bank_keyword, status, search_mode, active_only</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>목록(마스킹)</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>EDITOR</t>
+          <t>VIEWER</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>usp_finance_bank_save(U)</t>
+          <t>usp_finance_bank_list</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>UC-Bank-04</t>
+          <t>UC-Bank-01/06</t>
         </is>
       </c>
     </row>
@@ -10432,42 +10545,152 @@
           <t>은행/카드</t>
         </is>
       </c>
-      <c r="D95" s="14" t="inlineStr">
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>/finance/bank-accounts</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>은행계좌 또는 카드 등록(상호배타·중복 검증)</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Body: {bank_id, bank_name, bank_account? XOR card_number?, status}</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>EDITOR</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>usp_finance_bank_save(I)</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>UC-Bank-02/03</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>은행/카드</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>/finance/bank-accounts/{bankId}</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>은행/카드 수정/사용여부 변경</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Body: 수정필드</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>EDITOR</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>usp_finance_bank_save(U)</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>UC-Bank-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>은행/카드</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>/finance/bank-accounts/{bankId}</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>은행/카드 삭제(전표 참조 시 409)</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>Path: bankId</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>EDITOR</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
         <is>
           <t>usp_finance_bank_delete</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr">
+      <c r="K97" s="4" t="inlineStr">
         <is>
           <t>UC-Bank-05</t>
         </is>
